--- a/data/outputSpecialityRpt/File1/RPT_RPT9892372453518NR_outputSpecialityRpt.xlsx
+++ b/data/outputSpecialityRpt/File1/RPT_RPT9892372453518NR_outputSpecialityRpt.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Output| Specialty RPT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Output| Specialty RPT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -853,17 +853,17 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>00006022761</t>
+          <t>55513071001</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>ISENTRESS</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -877,51 +877,51 @@
         </is>
       </c>
       <c r="I15" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J15" s="14" t="n">
-        <v>0.1283553392116004</v>
+        <v>1.087715399391612</v>
       </c>
       <c r="K15" s="14" t="n">
-        <v>0.04261091291774269</v>
+        <v>1.117440559737953</v>
       </c>
       <c r="L15" s="14" t="n">
-        <v>0.038737949249435</v>
+        <v>1.15408913993337</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>0.03494344076258245</v>
+        <v>1.180407951520222</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>0.03149841962041426</v>
+        <v>1.206476747325211</v>
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>$22498.5615234375</t>
+          <t>$2250.52001953125</t>
         </is>
       </c>
       <c r="P15" s="14" t="inlineStr">
         <is>
-          <t>$1027.6101378199853</t>
+          <t>$2677.7881357857486</t>
         </is>
       </c>
       <c r="Q15" s="14" t="inlineStr">
         <is>
-          <t>$358.07035398654267</t>
+          <t>$2947.5037568743537</t>
         </is>
       </c>
       <c r="R15" s="14" t="inlineStr">
         <is>
-          <t>$340.92846305968885</t>
+          <t>$3254.133165424747</t>
         </is>
       </c>
       <c r="S15" s="14" t="inlineStr">
         <is>
-          <t>$321.3598001555064</t>
+          <t>$3550.6436968170055</t>
         </is>
       </c>
       <c r="T15" s="14" t="inlineStr">
         <is>
-          <t>$302.65667294509683</t>
+          <t>$3870.876210038308</t>
         </is>
       </c>
       <c r="U15" s="14" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>00069068803</t>
+          <t>50881001060</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>IBRANCE</t>
+          <t>JAKAFI</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -1017,101 +1017,101 @@
         </is>
       </c>
       <c r="I16" s="14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>3.3449530951237</v>
+        <v>1.145858896416911</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>2.163485356521457</v>
+        <v>1.211697203316414</v>
       </c>
       <c r="L16" s="14" t="n">
-        <v>2.155845260020467</v>
+        <v>0.8274801983109715</v>
       </c>
       <c r="M16" s="14" t="n">
-        <v>2.249000651476573</v>
+        <v>0.5975724033982286</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>2.372927021604775</v>
+        <v>0.5976987177066815</v>
       </c>
       <c r="O16" s="14" t="inlineStr">
         <is>
-          <t>$237052.796875</t>
+          <t>$21120.0</t>
         </is>
       </c>
       <c r="P16" s="14" t="inlineStr">
         <is>
-          <t>$204719.44600052293</t>
+          <t>$24439.516905267683</t>
         </is>
       </c>
       <c r="Q16" s="14" t="inlineStr">
         <is>
-          <t>$135831.32112443843</t>
+          <t>$26048.82092192574</t>
         </is>
       </c>
       <c r="R16" s="14" t="inlineStr">
         <is>
-          <t>$138858.2591317816</t>
+          <t>$17931.446710305077</t>
         </is>
       </c>
       <c r="S16" s="14" t="inlineStr">
         <is>
-          <t>$148619.1881682101</t>
+          <t>$13053.741698453368</t>
         </is>
       </c>
       <c r="T16" s="14" t="inlineStr">
         <is>
-          <t>$160855.98228830975</t>
+          <t>$13159.819330965986</t>
         </is>
       </c>
       <c r="U16" s="14" t="inlineStr">
         <is>
-          <t>$153539.5845003922</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="V16" s="14" t="inlineStr">
         <is>
-          <t>$135831.32112443843</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="W16" s="14" t="inlineStr">
         <is>
-          <t>$138858.2591317816</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="X16" s="14" t="inlineStr">
         <is>
-          <t>$148619.1881682101</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Y16" s="14" t="inlineStr">
         <is>
-          <t>$160855.98228830975</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Z16" s="14" t="inlineStr">
         <is>
-          <t>$103675.9232800745</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AA16" s="14" t="inlineStr">
         <is>
-          <t>$89408.86382623081</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AB16" s="14" t="inlineStr">
         <is>
-          <t>$89093.12683932808</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AC16" s="14" t="inlineStr">
         <is>
-          <t>$92942.89530865104</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AD16" s="14" t="inlineStr">
         <is>
-          <t>$98064.3147432094</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>49702022813</t>
+          <t>55513071021</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>TIVICAY</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1157,51 +1157,51 @@
         </is>
       </c>
       <c r="I17" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" s="14" t="n">
-        <v>1.710541571771106</v>
+        <v>3.263146198174836</v>
       </c>
       <c r="K17" s="14" t="n">
-        <v>1.291846107352441</v>
+        <v>3.352321679213858</v>
       </c>
       <c r="L17" s="14" t="n">
-        <v>0.1750918672408875</v>
+        <v>3.46226741980011</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>0.05299619075466232</v>
+        <v>3.541223854560666</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>0.01734337982544032</v>
+        <v>3.619430241975633</v>
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>$5580.3798828125</t>
+          <t>$6751.56005859375</t>
         </is>
       </c>
       <c r="P17" s="14" t="inlineStr">
         <is>
-          <t>$5172.624999821338</t>
+          <t>$8096.828648856414</t>
         </is>
       </c>
       <c r="Q17" s="14" t="inlineStr">
         <is>
-          <t>$4140.883210050301</t>
+          <t>$8735.780280560959</t>
         </is>
       </c>
       <c r="R17" s="14" t="inlineStr">
         <is>
-          <t>$592.8292244628137</t>
+          <t>$9476.00961080454</t>
         </is>
       </c>
       <c r="S17" s="14" t="inlineStr">
         <is>
-          <t>$188.72900858830204</t>
+          <t>$10180.055313600007</t>
         </is>
       </c>
       <c r="T17" s="14" t="inlineStr">
         <is>
-          <t>$64.95229067422413</t>
+          <t>$10927.107105537467</t>
         </is>
       </c>
       <c r="U17" s="14" t="inlineStr">
@@ -1273,17 +1273,17 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>50881000560</t>
+          <t>49702022813</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>JAKAFI</t>
+          <t>TIVICAY</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1297,51 +1297,51 @@
         </is>
       </c>
       <c r="I18" s="14" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>12.60444786058603</v>
+        <v>1.710541571771105</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>13.32866923648055</v>
+        <v>1.291846107352441</v>
       </c>
       <c r="L18" s="14" t="n">
-        <v>9.102282181420685</v>
+        <v>0.1750918672408875</v>
       </c>
       <c r="M18" s="14" t="n">
-        <v>6.573296437380515</v>
+        <v>0.05299619075466232</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>6.574685894773497</v>
+        <v>0.01734337982544032</v>
       </c>
       <c r="O18" s="14" t="inlineStr">
         <is>
-          <t>$253440.0</t>
+          <t>$5580.3798828125</t>
         </is>
       </c>
       <c r="P18" s="14" t="inlineStr">
         <is>
-          <t>$293274.20286321227</t>
+          <t>$5172.624999821337</t>
         </is>
       </c>
       <c r="Q18" s="14" t="inlineStr">
         <is>
-          <t>$312585.8510631089</t>
+          <t>$4140.883210050301</t>
         </is>
       </c>
       <c r="R18" s="14" t="inlineStr">
         <is>
-          <t>$215177.36052366093</t>
+          <t>$592.8292244628137</t>
         </is>
       </c>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>$156644.9003814404</t>
+          <t>$188.72900858830204</t>
         </is>
       </c>
       <c r="T18" s="14" t="inlineStr">
         <is>
-          <t>$157917.83197159186</t>
+          <t>$64.95229067422413</t>
         </is>
       </c>
       <c r="U18" s="14" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>50881001060</t>
+          <t>NEWGENERICS50881001060</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>JAKAFI</t>
+          <t>NEW GENERIC JAKAFI</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -1428,60 +1428,60 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I19" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="14" t="n">
-        <v>1.145858896416911</v>
+        <v>0</v>
       </c>
       <c r="K19" s="14" t="n">
-        <v>1.211697203316414</v>
+        <v>0</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>0.8274801983109715</v>
+        <v>0.4549518550318981</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>0.5975724033982286</v>
+        <v>0.7499507582363751</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>0.5976987177066815</v>
+        <v>0.8203542280503033</v>
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>$21120.0</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P19" s="14" t="inlineStr">
         <is>
-          <t>$24439.516905267687</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q19" s="14" t="inlineStr">
         <is>
-          <t>$26048.82092192574</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R19" s="14" t="inlineStr">
         <is>
-          <t>$17931.446710305077</t>
+          <t>$8868.30986390438</t>
         </is>
       </c>
       <c r="S19" s="14" t="inlineStr">
         <is>
-          <t>$13053.741698453368</t>
+          <t>$14731.682667945546</t>
         </is>
       </c>
       <c r="T19" s="14" t="inlineStr">
         <is>
-          <t>$13159.819330965986</t>
+          <t>$16239.221856890927</t>
         </is>
       </c>
       <c r="U19" s="14" t="inlineStr">
@@ -1553,75 +1553,75 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>55513071001</t>
+          <t>NEWGENERICS59676056201</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>PROLIA</t>
+          <t>NEW GENERIC PREZISTA</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>HIV-PROTEASE INHIBITOR</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I20" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>1.087715399391612</v>
+        <v>1.757575546613665</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>1.117440559737953</v>
+        <v>1.747712215571186</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>1.15408913993337</v>
+        <v>1.746971797815821</v>
       </c>
       <c r="M20" s="14" t="n">
-        <v>1.180407951520222</v>
+        <v>1.732917767299732</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>1.206476747325211</v>
+        <v>1.715889183705748</v>
       </c>
       <c r="O20" s="14" t="inlineStr">
         <is>
-          <t>$2250.52001953125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P20" s="14" t="inlineStr">
         <is>
-          <t>$2677.7881357857495</t>
+          <t>$12999.891963501601</t>
         </is>
       </c>
       <c r="Q20" s="14" t="inlineStr">
         <is>
-          <t>$2947.5037568743537</t>
+          <t>$13522.352683530904</t>
         </is>
       </c>
       <c r="R20" s="14" t="inlineStr">
         <is>
-          <t>$3254.133165424747</t>
+          <t>$14141.200102029135</t>
         </is>
       </c>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>$3550.6436968170055</t>
+          <t>$14703.278958525229</t>
         </is>
       </c>
       <c r="T20" s="14" t="inlineStr">
         <is>
-          <t>$3870.876210038308</t>
+          <t>$15260.23943911953</t>
         </is>
       </c>
       <c r="U20" s="14" t="inlineStr">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>55513071021</t>
+          <t>50881000560</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>PROLIA</t>
+          <t>JAKAFI</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1717,51 +1717,51 @@
         </is>
       </c>
       <c r="I21" s="14" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J21" s="14" t="n">
-        <v>3.263146198174836</v>
+        <v>12.60444786058602</v>
       </c>
       <c r="K21" s="14" t="n">
-        <v>3.352321679213858</v>
+        <v>13.32866923648055</v>
       </c>
       <c r="L21" s="14" t="n">
-        <v>3.46226741980011</v>
+        <v>9.102282181420685</v>
       </c>
       <c r="M21" s="14" t="n">
-        <v>3.541223854560666</v>
+        <v>6.573296437380515</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>3.619430241975633</v>
+        <v>6.574685894773497</v>
       </c>
       <c r="O21" s="14" t="inlineStr">
         <is>
-          <t>$6751.56005859375</t>
+          <t>$253440.0</t>
         </is>
       </c>
       <c r="P21" s="14" t="inlineStr">
         <is>
-          <t>$8096.828648856415</t>
+          <t>$293274.2028632122</t>
         </is>
       </c>
       <c r="Q21" s="14" t="inlineStr">
         <is>
-          <t>$8735.780280560959</t>
+          <t>$312585.8510631089</t>
         </is>
       </c>
       <c r="R21" s="14" t="inlineStr">
         <is>
-          <t>$9476.00961080454</t>
+          <t>$215177.36052366093</t>
         </is>
       </c>
       <c r="S21" s="14" t="inlineStr">
         <is>
-          <t>$10180.055313600007</t>
+          <t>$156644.9003814404</t>
         </is>
       </c>
       <c r="T21" s="14" t="inlineStr">
         <is>
-          <t>$10927.107105537467</t>
+          <t>$157917.83197159186</t>
         </is>
       </c>
       <c r="U21" s="14" t="inlineStr">
@@ -1833,125 +1833,125 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>58406003204</t>
+          <t>NEWGENERICS00006022761</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>ENBREL SURECLICK</t>
+          <t>NEW GENERIC ISENTRESS</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I22" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>3.136542659093069</v>
+        <v>2.402483852304173</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>3.1995199036461</v>
+        <v>2.261235393576385</v>
       </c>
       <c r="L22" s="14" t="n">
-        <v>3.292139364772318</v>
+        <v>2.059957414033209</v>
       </c>
       <c r="M22" s="14" t="n">
-        <v>3.365994951517328</v>
+        <v>1.853208273952968</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>3.439083863984076</v>
+        <v>1.664215032205805</v>
       </c>
       <c r="O22" s="14" t="inlineStr">
         <is>
-          <t>$88102.078125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P22" s="14" t="inlineStr">
         <is>
-          <t>$95126.18391696518</t>
+          <t>$17310.1362551156</t>
         </is>
       </c>
       <c r="Q22" s="14" t="inlineStr">
         <is>
-          <t>$99542.96941592282</t>
+          <t>$17097.419519245028</t>
         </is>
       </c>
       <c r="R22" s="14" t="inlineStr">
         <is>
-          <t>$105078.08601250713</t>
+          <t>$16308.070340477361</t>
         </is>
       </c>
       <c r="S22" s="14" t="inlineStr">
         <is>
-          <t>$110224.6109447186</t>
+          <t>$15325.873543642638</t>
         </is>
       </c>
       <c r="T22" s="14" t="inlineStr">
         <is>
-          <t>$115524.84981768658</t>
+          <t>$14376.961881517107</t>
         </is>
       </c>
       <c r="U22" s="14" t="inlineStr">
         <is>
-          <t>$95126.18391696518</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="V22" s="14" t="inlineStr">
         <is>
-          <t>$99542.96941592282</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="W22" s="14" t="inlineStr">
         <is>
-          <t>$105078.08601250713</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="X22" s="14" t="inlineStr">
         <is>
-          <t>$110224.6109447186</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Y22" s="14" t="inlineStr">
         <is>
-          <t>$115524.84981768658</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Z22" s="14" t="inlineStr">
         <is>
-          <t>$21972.117342521185</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AA22" s="14" t="inlineStr">
         <is>
-          <t>$22413.28571088891</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AB22" s="14" t="inlineStr">
         <is>
-          <t>$23062.10381708192</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AC22" s="14" t="inlineStr">
         <is>
-          <t>$23579.477178371166</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AD22" s="14" t="inlineStr">
         <is>
-          <t>$24091.479830878052</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -1973,75 +1973,75 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>59676056201</t>
+          <t>NEWGENERICS50881000560</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>PREZISTA</t>
+          <t>NEW GENERIC JAKAFI</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>HIV-PROTEASE INHIBITOR</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I23" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J23" s="14" t="n">
-        <v>1.217636307946205</v>
+        <v>0</v>
       </c>
       <c r="K23" s="14" t="n">
-        <v>1.215785760809346</v>
+        <v>0</v>
       </c>
       <c r="L23" s="14" t="n">
-        <v>1.212764132761546</v>
+        <v>5.00447040535088</v>
       </c>
       <c r="M23" s="14" t="n">
-        <v>1.206233697668001</v>
+        <v>8.249458340600127</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>1.198893559355905</v>
+        <v>9.023896508553337</v>
       </c>
       <c r="O23" s="14" t="inlineStr">
         <is>
-          <t>$23308.01953125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P23" s="14" t="inlineStr">
         <is>
-          <t>$10007.319450092597</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q23" s="14" t="inlineStr">
         <is>
-          <t>$10454.472460865267</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R23" s="14" t="inlineStr">
         <is>
-          <t>$10913.373505145259</t>
+          <t>$106419.71836685255</t>
         </is>
       </c>
       <c r="S23" s="14" t="inlineStr">
         <is>
-          <t>$11381.318433353297</t>
+          <t>$176780.19201534655</t>
         </is>
       </c>
       <c r="T23" s="14" t="inlineStr">
         <is>
-          <t>$11859.231501773562</t>
+          <t>$194870.6622826911</t>
         </is>
       </c>
       <c r="U23" s="14" t="inlineStr">
@@ -2113,17 +2113,17 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>61958190101</t>
+          <t>00006022761</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>GENVOYA</t>
+          <t>ISENTRESS</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>HIV-MULTICLASS COMBO</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -2140,48 +2140,48 @@
         <v>3</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>3.270716223539261</v>
+        <v>0.1283553392116003</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>3.41495505859339</v>
+        <v>0.04261091291774269</v>
       </c>
       <c r="L24" s="14" t="n">
-        <v>3.56498375485787</v>
+        <v>0.038737949249435</v>
       </c>
       <c r="M24" s="14" t="n">
-        <v>3.713720334748027</v>
+        <v>0.03494344076258245</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>3.865938081037455</v>
+        <v>0.03149841962041426</v>
       </c>
       <c r="O24" s="14" t="inlineStr">
         <is>
-          <t>$45533.8798828125</t>
+          <t>$22498.5615234375</t>
         </is>
       </c>
       <c r="P24" s="14" t="inlineStr">
         <is>
-          <t>$53238.015893742464</t>
+          <t>$1027.610137819985</t>
         </is>
       </c>
       <c r="Q24" s="14" t="inlineStr">
         <is>
-          <t>$58719.50915449923</t>
+          <t>$358.07035398654267</t>
         </is>
       </c>
       <c r="R24" s="14" t="inlineStr">
         <is>
-          <t>$64759.67692795637</t>
+          <t>$340.92846305968885</t>
         </is>
       </c>
       <c r="S24" s="14" t="inlineStr">
         <is>
-          <t>$71273.65240556835</t>
+          <t>$321.3598001555064</t>
         </is>
       </c>
       <c r="T24" s="14" t="inlineStr">
         <is>
-          <t>$78376.1223346196</t>
+          <t>$302.65667294509683</t>
         </is>
       </c>
       <c r="U24" s="14" t="inlineStr">
@@ -2253,125 +2253,125 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS00006022761</t>
+          <t>58406003204</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC ISENTRESS</t>
+          <t>ENBREL SURECLICK</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I25" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>2.402483852304172</v>
+        <v>3.136542659093068</v>
       </c>
       <c r="K25" s="14" t="n">
-        <v>2.261235393576386</v>
+        <v>3.1995199036461</v>
       </c>
       <c r="L25" s="14" t="n">
-        <v>2.059957414033208</v>
+        <v>3.292139364772318</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>1.853208273952968</v>
+        <v>3.365994951517328</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>1.664215032205805</v>
+        <v>3.439083863984076</v>
       </c>
       <c r="O25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$88102.078125</t>
         </is>
       </c>
       <c r="P25" s="14" t="inlineStr">
         <is>
-          <t>$17310.136255115598</t>
+          <t>$95126.18391696515</t>
         </is>
       </c>
       <c r="Q25" s="14" t="inlineStr">
         <is>
-          <t>$17097.419519245028</t>
+          <t>$99542.96941592282</t>
         </is>
       </c>
       <c r="R25" s="14" t="inlineStr">
         <is>
-          <t>$16308.070340477361</t>
+          <t>$105078.08601250713</t>
         </is>
       </c>
       <c r="S25" s="14" t="inlineStr">
         <is>
-          <t>$15325.873543642638</t>
+          <t>$110224.6109447186</t>
         </is>
       </c>
       <c r="T25" s="14" t="inlineStr">
         <is>
-          <t>$14376.961881517107</t>
+          <t>$115524.84981768658</t>
         </is>
       </c>
       <c r="U25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$95126.18391696515</t>
         </is>
       </c>
       <c r="V25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$99542.96941592282</t>
         </is>
       </c>
       <c r="W25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$105078.08601250713</t>
         </is>
       </c>
       <c r="X25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$110224.6109447186</t>
         </is>
       </c>
       <c r="Y25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$115524.84981768658</t>
         </is>
       </c>
       <c r="Z25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$21972.117342521182</t>
         </is>
       </c>
       <c r="AA25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$22413.28571088891</t>
         </is>
       </c>
       <c r="AB25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$23062.10381708192</t>
         </is>
       </c>
       <c r="AC25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$23579.477178371166</t>
         </is>
       </c>
       <c r="AD25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$24091.479830878052</t>
         </is>
       </c>
     </row>
@@ -2393,12 +2393,12 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS00069068803</t>
+          <t>00069068803</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC IBRANCE</t>
+          <t>IBRANCE</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2408,110 +2408,110 @@
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I26" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>1.220712473031184</v>
+        <v>3.344953095123699</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>2.633963535973004</v>
+        <v>2.163485356521457</v>
       </c>
       <c r="L26" s="14" t="n">
-        <v>2.955003500285743</v>
+        <v>2.155845260020467</v>
       </c>
       <c r="M26" s="14" t="n">
-        <v>3.138408969495659</v>
+        <v>2.249000651476573</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>3.298879475272806</v>
+        <v>2.372927021604775</v>
       </c>
       <c r="O26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$237052.796875</t>
         </is>
       </c>
       <c r="P26" s="14" t="inlineStr">
         <is>
-          <t>$67236.9516240519</t>
+          <t>$204719.4460005229</t>
         </is>
       </c>
       <c r="Q26" s="14" t="inlineStr">
         <is>
-          <t>$148796.59389993534</t>
+          <t>$135831.32112443843</t>
         </is>
       </c>
       <c r="R26" s="14" t="inlineStr">
         <is>
-          <t>$171210.27686069216</t>
+          <t>$138858.2591317816</t>
         </is>
       </c>
       <c r="S26" s="14" t="inlineStr">
         <is>
-          <t>$186496.1903254034</t>
+          <t>$148619.1881682101</t>
         </is>
       </c>
       <c r="T26" s="14" t="inlineStr">
         <is>
-          <t>$201055.27665775226</t>
+          <t>$160855.98228830975</t>
         </is>
       </c>
       <c r="U26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$153539.58450039217</t>
         </is>
       </c>
       <c r="V26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$135831.32112443843</t>
         </is>
       </c>
       <c r="W26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$138858.2591317816</t>
         </is>
       </c>
       <c r="X26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$148619.1881682101</t>
         </is>
       </c>
       <c r="Y26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$160855.98228830975</t>
         </is>
       </c>
       <c r="Z26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$103675.92328007446</t>
         </is>
       </c>
       <c r="AA26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$89408.86382623081</t>
         </is>
       </c>
       <c r="AB26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$89093.12683932808</t>
         </is>
       </c>
       <c r="AC26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$92942.89530865104</t>
         </is>
       </c>
       <c r="AD26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$98064.3147432094</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS49702022813</t>
+          <t>NEWGENERICS00069068803</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC TIVICAY</t>
+          <t>NEW GENERIC IBRANCE</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
@@ -2560,19 +2560,19 @@
         <v>0</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>0</v>
+        <v>1.220712473031184</v>
       </c>
       <c r="K27" s="14" t="n">
-        <v>0.2672832312894735</v>
+        <v>2.633963535973004</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>1.226480217858823</v>
+        <v>2.955003500285744</v>
       </c>
       <c r="M27" s="14" t="n">
-        <v>1.206335621863995</v>
+        <v>3.138408969495659</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>1.113049337610308</v>
+        <v>3.298879475272806</v>
       </c>
       <c r="O27" s="14" t="inlineStr">
         <is>
@@ -2581,27 +2581,27 @@
       </c>
       <c r="P27" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$67236.95162405192</t>
         </is>
       </c>
       <c r="Q27" s="14" t="inlineStr">
         <is>
-          <t>$770.8878143009053</t>
+          <t>$148796.59389993534</t>
         </is>
       </c>
       <c r="R27" s="14" t="inlineStr">
         <is>
-          <t>$3735.440965998716</t>
+          <t>$171210.27686069216</t>
         </is>
       </c>
       <c r="S27" s="14" t="inlineStr">
         <is>
-          <t>$3863.1118364416648</t>
+          <t>$186496.1903254034</t>
         </is>
       </c>
       <c r="T27" s="14" t="inlineStr">
         <is>
-          <t>$3747.756305950539</t>
+          <t>$201055.27665775226</t>
         </is>
       </c>
       <c r="U27" s="14" t="inlineStr">
@@ -2673,75 +2673,75 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS50881000560</t>
+          <t>59676056201</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC JAKAFI</t>
+          <t>PREZISTA</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>HIV-PROTEASE INHIBITOR</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I28" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>0</v>
+        <v>1.217636307946204</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>0</v>
+        <v>1.215785760809346</v>
       </c>
       <c r="L28" s="14" t="n">
-        <v>5.004470405350879</v>
+        <v>1.212764132761546</v>
       </c>
       <c r="M28" s="14" t="n">
-        <v>8.249458340600127</v>
+        <v>1.206233697668001</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>9.023896508553335</v>
+        <v>1.198893559355905</v>
       </c>
       <c r="O28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$23308.01953125</t>
         </is>
       </c>
       <c r="P28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$10007.319450092593</t>
         </is>
       </c>
       <c r="Q28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$10454.472460865267</t>
         </is>
       </c>
       <c r="R28" s="14" t="inlineStr">
         <is>
-          <t>$106419.71836685255</t>
+          <t>$10913.373505145259</t>
         </is>
       </c>
       <c r="S28" s="14" t="inlineStr">
         <is>
-          <t>$176780.19201534655</t>
+          <t>$11381.318433353297</t>
         </is>
       </c>
       <c r="T28" s="14" t="inlineStr">
         <is>
-          <t>$194870.6622826911</t>
+          <t>$11859.231501773562</t>
         </is>
       </c>
       <c r="U28" s="14" t="inlineStr">
@@ -2813,75 +2813,75 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS50881001060</t>
+          <t>61958190101</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC JAKAFI</t>
+          <t>GENVOYA</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>HIV-MULTICLASS COMBO</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I29" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>0</v>
+        <v>3.270716223539261</v>
       </c>
       <c r="K29" s="14" t="n">
-        <v>0</v>
+        <v>3.41495505859339</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>0.454951855031898</v>
+        <v>3.56498375485787</v>
       </c>
       <c r="M29" s="14" t="n">
-        <v>0.7499507582363751</v>
+        <v>3.713720334748027</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>0.8203542280503031</v>
+        <v>3.865938081037455</v>
       </c>
       <c r="O29" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$45533.8798828125</t>
         </is>
       </c>
       <c r="P29" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$53238.01589374245</t>
         </is>
       </c>
       <c r="Q29" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$58719.50915449923</t>
         </is>
       </c>
       <c r="R29" s="14" t="inlineStr">
         <is>
-          <t>$8868.30986390438</t>
+          <t>$64759.67692795637</t>
         </is>
       </c>
       <c r="S29" s="14" t="inlineStr">
         <is>
-          <t>$14731.682667945546</t>
+          <t>$71273.65240556835</t>
         </is>
       </c>
       <c r="T29" s="14" t="inlineStr">
         <is>
-          <t>$16239.221856890927</t>
+          <t>$78376.1223346196</t>
         </is>
       </c>
       <c r="U29" s="14" t="inlineStr">
@@ -2953,17 +2953,17 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS59676056201</t>
+          <t>NEWGENERICS49702022813</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC PREZISTA</t>
+          <t>NEW GENERIC TIVICAY</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>HIV-PROTEASE INHIBITOR</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2980,19 +2980,19 @@
         <v>0</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>1.757575546613664</v>
+        <v>0</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>1.747712215571186</v>
+        <v>0.2672832312894735</v>
       </c>
       <c r="L30" s="14" t="n">
-        <v>1.74697179781582</v>
+        <v>1.226480217858823</v>
       </c>
       <c r="M30" s="14" t="n">
-        <v>1.732917767299732</v>
+        <v>1.206335621863995</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>1.715889183705748</v>
+        <v>1.113049337610308</v>
       </c>
       <c r="O30" s="14" t="inlineStr">
         <is>
@@ -3001,27 +3001,27 @@
       </c>
       <c r="P30" s="14" t="inlineStr">
         <is>
-          <t>$12999.891963501597</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q30" s="14" t="inlineStr">
         <is>
-          <t>$13522.352683530904</t>
+          <t>$770.8878143009053</t>
         </is>
       </c>
       <c r="R30" s="14" t="inlineStr">
         <is>
-          <t>$14141.200102029135</t>
+          <t>$3735.440965998716</t>
         </is>
       </c>
       <c r="S30" s="14" t="inlineStr">
         <is>
-          <t>$14703.278958525229</t>
+          <t>$3863.1118364416648</t>
         </is>
       </c>
       <c r="T30" s="14" t="inlineStr">
         <is>
-          <t>$15260.23943911953</t>
+          <t>$3747.756305950539</t>
         </is>
       </c>
       <c r="U30" s="14" t="inlineStr">
